--- a/templates/Fiche d'identité des entreprises/master.xlsx
+++ b/templates/Fiche d'identité des entreprises/master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosch\Bureau\KAIVAA\kaivaa-builder\templates\BenchmarkV3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosch\Bureau\KAIVAA\kaivaa-builder\templates\Fiche d'identité des entreprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434F84DF-3986-4BD8-94E5-8538E4B79926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC591E-DBBD-47F0-8B0F-63361337E1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
+    <workbookView xWindow="4155" yWindow="4155" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
   </bookViews>
   <sheets>
     <sheet name="DONNÉES BRUTES" sheetId="26" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Listes" sheetId="10" r:id="rId4"/>
     <sheet name="Image" sheetId="47" r:id="rId5"/>
     <sheet name="Balises" sheetId="9" r:id="rId6"/>
-    <sheet name="Charts_settings" sheetId="5" r:id="rId7"/>
+    <sheet name="Boucles" sheetId="5" r:id="rId7"/>
     <sheet name="Analyse" sheetId="46" r:id="rId8"/>
     <sheet name="Table" sheetId="36" r:id="rId9"/>
   </sheets>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="Années">_xlfn.ANCHORARRAY(Listes!$H$11)</definedName>
     <definedName name="Entreprise">Balises!$E$6</definedName>
-    <definedName name="Loop_parameters">Charts_settings!$B$6:$E$6</definedName>
+    <definedName name="Loop_parameters">Boucles!$B$6:$E$6</definedName>
     <definedName name="Périodes">Balises!$E$6</definedName>
-    <definedName name="s_produit">Charts_settings!$E$6</definedName>
+    <definedName name="s_produit">Boucles!$E$6</definedName>
     <definedName name="siren">Balises!$E$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="E19" s="20">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>45935</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
